--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -6560,10 +6560,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118484220</v>
+        <v>118483536</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>57659</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6572,46 +6572,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>338502</v>
+        <v>338450</v>
       </c>
       <c r="R51" t="n">
-        <v>6433373</v>
+        <v>6433426</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6638,17 +6642,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6657,19 +6656,18 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6788,7 +6786,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118484488</v>
+        <v>118484390</v>
       </c>
       <c r="B53" t="n">
         <v>57306</v>
@@ -6832,10 +6830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>338279</v>
+        <v>338446</v>
       </c>
       <c r="R53" t="n">
-        <v>6433349</v>
+        <v>6433213</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6862,17 +6860,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
+          <t>Färskt spår av födosökande spillkråka på tallved.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6899,10 +6897,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118484390</v>
+        <v>118484220</v>
       </c>
       <c r="B54" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6911,31 +6909,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6943,10 +6945,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>338446</v>
+        <v>338502</v>
       </c>
       <c r="R54" t="n">
-        <v>6433213</v>
+        <v>6433373</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6983,7 +6985,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tallved.</t>
+          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6992,6 +6994,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7010,10 +7013,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118484661</v>
+        <v>118484328</v>
       </c>
       <c r="B55" t="n">
-        <v>96114</v>
+        <v>58133</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7026,27 +7029,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2569</v>
+        <v>208249</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7054,10 +7062,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>338511</v>
+        <v>338417</v>
       </c>
       <c r="R55" t="n">
-        <v>6433435</v>
+        <v>6433248</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7090,11 +7098,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7122,10 +7125,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118484237</v>
+        <v>118484672</v>
       </c>
       <c r="B56" t="n">
-        <v>58133</v>
+        <v>94620</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7138,46 +7141,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>338256</v>
+        <v>338400</v>
       </c>
       <c r="R56" t="n">
-        <v>6433432</v>
+        <v>6433392</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7201,12 +7203,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7222,22 +7229,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118483536</v>
+        <v>118484488</v>
       </c>
       <c r="B57" t="n">
-        <v>57659</v>
+        <v>57306</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7246,20 +7253,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7267,29 +7274,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>338450</v>
+        <v>338279</v>
       </c>
       <c r="R57" t="n">
-        <v>6433426</v>
+        <v>6433349</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7324,6 +7323,11 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7336,22 +7340,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118483227</v>
+        <v>118483185</v>
       </c>
       <c r="B58" t="n">
-        <v>57443</v>
+        <v>57933</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7360,25 +7364,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>103042</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7400,10 +7404,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>338294</v>
+        <v>338304</v>
       </c>
       <c r="R58" t="n">
-        <v>6433559</v>
+        <v>6433539</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7462,10 +7466,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118483185</v>
+        <v>118484237</v>
       </c>
       <c r="B59" t="n">
-        <v>57933</v>
+        <v>58133</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7474,25 +7478,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103042</v>
+        <v>208249</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7500,13 +7504,10 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7514,13 +7515,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>338304</v>
+        <v>338256</v>
       </c>
       <c r="R59" t="n">
-        <v>6433539</v>
+        <v>6433432</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7544,12 +7545,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7558,6 +7559,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7576,10 +7578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118484328</v>
+        <v>118483227</v>
       </c>
       <c r="B60" t="n">
-        <v>58133</v>
+        <v>57443</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7588,25 +7590,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7614,10 +7616,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7625,10 +7630,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>338417</v>
+        <v>338294</v>
       </c>
       <c r="R60" t="n">
-        <v>6433248</v>
+        <v>6433559</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7655,12 +7660,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7669,7 +7674,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7688,10 +7692,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118484672</v>
+        <v>118484661</v>
       </c>
       <c r="B61" t="n">
-        <v>94620</v>
+        <v>96114</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7704,42 +7708,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>338400</v>
+        <v>338511</v>
       </c>
       <c r="R61" t="n">
-        <v>6433392</v>
+        <v>6433435</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7766,17 +7766,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
+          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7792,12 +7792,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -6560,10 +6560,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118483536</v>
+        <v>118484328</v>
       </c>
       <c r="B51" t="n">
-        <v>57659</v>
+        <v>58133</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>208249</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6598,13 +6598,10 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6612,10 +6609,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>338450</v>
+        <v>338417</v>
       </c>
       <c r="R51" t="n">
-        <v>6433426</v>
+        <v>6433248</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6642,12 +6639,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6656,6 +6653,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6786,10 +6784,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118484390</v>
+        <v>118484661</v>
       </c>
       <c r="B53" t="n">
-        <v>57306</v>
+        <v>96114</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6798,42 +6796,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>338446</v>
+        <v>338511</v>
       </c>
       <c r="R53" t="n">
-        <v>6433213</v>
+        <v>6433435</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6860,17 +6858,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tallved.</t>
+          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6879,28 +6877,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118484220</v>
+        <v>118484390</v>
       </c>
       <c r="B54" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6909,35 +6908,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6945,10 +6940,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>338502</v>
+        <v>338446</v>
       </c>
       <c r="R54" t="n">
-        <v>6433373</v>
+        <v>6433213</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6985,7 +6980,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
+          <t>Färskt spår av födosökande spillkråka på tallved.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6994,7 +6989,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7013,10 +7007,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118484328</v>
+        <v>118484672</v>
       </c>
       <c r="B55" t="n">
-        <v>58133</v>
+        <v>94620</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7029,43 +7023,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>338417</v>
+        <v>338400</v>
       </c>
       <c r="R55" t="n">
-        <v>6433248</v>
+        <v>6433392</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7092,12 +7085,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7113,22 +7111,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118484672</v>
+        <v>118484220</v>
       </c>
       <c r="B56" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7137,30 +7135,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -7173,10 +7171,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>338400</v>
+        <v>338502</v>
       </c>
       <c r="R56" t="n">
-        <v>6433392</v>
+        <v>6433373</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7213,7 +7211,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
+          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7241,10 +7239,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118484488</v>
+        <v>118483185</v>
       </c>
       <c r="B57" t="n">
-        <v>57306</v>
+        <v>57933</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7253,20 +7251,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7274,21 +7272,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>338279</v>
+        <v>338304</v>
       </c>
       <c r="R57" t="n">
-        <v>6433349</v>
+        <v>6433539</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7315,17 +7321,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7340,22 +7341,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118483185</v>
+        <v>118483227</v>
       </c>
       <c r="B58" t="n">
-        <v>57933</v>
+        <v>57443</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7364,25 +7365,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7404,10 +7405,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>338304</v>
+        <v>338294</v>
       </c>
       <c r="R58" t="n">
-        <v>6433539</v>
+        <v>6433559</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7578,10 +7579,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118483227</v>
+        <v>118484488</v>
       </c>
       <c r="B60" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7594,46 +7595,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>338294</v>
+        <v>338279</v>
       </c>
       <c r="R60" t="n">
-        <v>6433559</v>
+        <v>6433349</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7660,12 +7653,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7680,22 +7678,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118484661</v>
+        <v>118483536</v>
       </c>
       <c r="B61" t="n">
-        <v>96114</v>
+        <v>57659</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7708,27 +7706,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7736,10 +7742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>338511</v>
+        <v>338450</v>
       </c>
       <c r="R61" t="n">
-        <v>6433435</v>
+        <v>6433426</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7766,17 +7772,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Större tuvor</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7785,7 +7786,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -6447,7 +6447,7 @@
         <v>118420569</v>
       </c>
       <c r="B50" t="n">
-        <v>94620</v>
+        <v>94627</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6560,10 +6560,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118484328</v>
+        <v>118484220</v>
       </c>
       <c r="B51" t="n">
-        <v>58133</v>
+        <v>97853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6572,47 +6572,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>338417</v>
+        <v>338502</v>
       </c>
       <c r="R51" t="n">
-        <v>6433248</v>
+        <v>6433373</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6639,12 +6638,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6660,22 +6664,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118484616</v>
+        <v>118484328</v>
       </c>
       <c r="B52" t="n">
-        <v>96114</v>
+        <v>58133</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6688,27 +6692,32 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2569</v>
+        <v>208249</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6716,10 +6725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>338516</v>
+        <v>338417</v>
       </c>
       <c r="R52" t="n">
-        <v>6433261</v>
+        <v>6433248</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6752,11 +6761,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6784,10 +6788,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118484661</v>
+        <v>118483185</v>
       </c>
       <c r="B53" t="n">
-        <v>96114</v>
+        <v>57933</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6796,31 +6800,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2569</v>
+        <v>103042</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6828,10 +6840,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>338511</v>
+        <v>338304</v>
       </c>
       <c r="R53" t="n">
-        <v>6433435</v>
+        <v>6433539</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6858,17 +6870,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Större tuvor</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6877,7 +6884,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6896,10 +6902,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118484390</v>
+        <v>118484661</v>
       </c>
       <c r="B54" t="n">
-        <v>57306</v>
+        <v>96121</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6908,42 +6914,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>338446</v>
+        <v>338511</v>
       </c>
       <c r="R54" t="n">
-        <v>6433213</v>
+        <v>6433435</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6970,17 +6976,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tallved.</t>
+          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6989,28 +6995,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118484672</v>
+        <v>118484616</v>
       </c>
       <c r="B55" t="n">
-        <v>94620</v>
+        <v>96121</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7023,42 +7030,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>338400</v>
+        <v>338516</v>
       </c>
       <c r="R55" t="n">
-        <v>6433392</v>
+        <v>6433261</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7085,17 +7088,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
+          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7111,22 +7114,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118484220</v>
+        <v>118483227</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7135,46 +7138,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>338502</v>
+        <v>338294</v>
       </c>
       <c r="R56" t="n">
-        <v>6433373</v>
+        <v>6433559</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7201,17 +7208,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7220,29 +7222,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118483185</v>
+        <v>118484488</v>
       </c>
       <c r="B57" t="n">
-        <v>57933</v>
+        <v>57306</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7251,20 +7252,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7272,29 +7273,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>338304</v>
+        <v>338279</v>
       </c>
       <c r="R57" t="n">
-        <v>6433539</v>
+        <v>6433349</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7321,12 +7314,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7341,22 +7339,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118483227</v>
+        <v>118483536</v>
       </c>
       <c r="B58" t="n">
-        <v>57443</v>
+        <v>57659</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7365,25 +7363,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7405,10 +7403,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>338294</v>
+        <v>338450</v>
       </c>
       <c r="R58" t="n">
-        <v>6433559</v>
+        <v>6433426</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7435,12 +7433,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7467,10 +7465,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118484237</v>
+        <v>118484672</v>
       </c>
       <c r="B59" t="n">
-        <v>58133</v>
+        <v>94627</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7483,46 +7481,45 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>338256</v>
+        <v>338400</v>
       </c>
       <c r="R59" t="n">
-        <v>6433432</v>
+        <v>6433392</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7546,12 +7543,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7567,22 +7569,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118484488</v>
+        <v>118484237</v>
       </c>
       <c r="B60" t="n">
-        <v>57306</v>
+        <v>58133</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7591,45 +7593,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>208249</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>338279</v>
+        <v>338256</v>
       </c>
       <c r="R60" t="n">
-        <v>6433349</v>
+        <v>6433432</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7653,17 +7660,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7672,28 +7674,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118483536</v>
+        <v>118484390</v>
       </c>
       <c r="B61" t="n">
-        <v>57659</v>
+        <v>57306</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7702,20 +7705,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7723,29 +7726,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>338450</v>
+        <v>338446</v>
       </c>
       <c r="R61" t="n">
-        <v>6433426</v>
+        <v>6433213</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7772,12 +7767,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på tallved.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7792,12 +7792,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -6560,10 +6560,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118484220</v>
+        <v>118483536</v>
       </c>
       <c r="B51" t="n">
-        <v>97853</v>
+        <v>57659</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6572,46 +6572,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>338502</v>
+        <v>338450</v>
       </c>
       <c r="R51" t="n">
-        <v>6433373</v>
+        <v>6433426</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6638,17 +6642,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6657,29 +6656,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118484328</v>
+        <v>118484661</v>
       </c>
       <c r="B52" t="n">
-        <v>58133</v>
+        <v>96121</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6692,32 +6690,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>208249</v>
+        <v>2569</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6725,10 +6718,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>338417</v>
+        <v>338511</v>
       </c>
       <c r="R52" t="n">
-        <v>6433248</v>
+        <v>6433435</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6761,6 +6754,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6788,10 +6786,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118483185</v>
+        <v>118484616</v>
       </c>
       <c r="B53" t="n">
-        <v>57933</v>
+        <v>96121</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6800,39 +6798,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103042</v>
+        <v>2569</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6840,10 +6830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>338304</v>
+        <v>338516</v>
       </c>
       <c r="R53" t="n">
-        <v>6433539</v>
+        <v>6433261</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6870,12 +6860,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6884,6 +6879,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6902,10 +6898,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118484661</v>
+        <v>118483185</v>
       </c>
       <c r="B54" t="n">
-        <v>96121</v>
+        <v>57933</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6914,31 +6910,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2569</v>
+        <v>103042</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6946,10 +6950,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>338511</v>
+        <v>338304</v>
       </c>
       <c r="R54" t="n">
-        <v>6433435</v>
+        <v>6433539</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6976,17 +6980,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Större tuvor</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6995,7 +6994,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7014,10 +7012,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118484616</v>
+        <v>118484328</v>
       </c>
       <c r="B55" t="n">
-        <v>96121</v>
+        <v>58133</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7030,27 +7028,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2569</v>
+        <v>208249</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7058,10 +7061,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>338516</v>
+        <v>338417</v>
       </c>
       <c r="R55" t="n">
-        <v>6433261</v>
+        <v>6433248</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7094,11 +7097,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Större tuvor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7126,10 +7124,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118483227</v>
+        <v>118484390</v>
       </c>
       <c r="B56" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7142,46 +7140,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>338294</v>
+        <v>338446</v>
       </c>
       <c r="R56" t="n">
-        <v>6433559</v>
+        <v>6433213</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7208,12 +7198,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka på tallved.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7228,22 +7223,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118484488</v>
+        <v>118484220</v>
       </c>
       <c r="B57" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7252,31 +7247,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7284,10 +7283,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>338279</v>
+        <v>338502</v>
       </c>
       <c r="R57" t="n">
-        <v>6433349</v>
+        <v>6433373</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7314,17 +7313,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
+          <t>Ca 20 plantor i äldre barrblandskog på yta av 3x4m</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7333,6 +7332,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7351,10 +7351,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118483536</v>
+        <v>118484488</v>
       </c>
       <c r="B58" t="n">
-        <v>57659</v>
+        <v>57306</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7363,20 +7363,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7384,29 +7384,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skår, Vg</t>
+          <t>Angertuvan - Risveden, Vg</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>338450</v>
+        <v>338279</v>
       </c>
       <c r="R58" t="n">
-        <v>6433426</v>
+        <v>6433349</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7441,6 +7433,11 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färskt spår av födosökande spillkråka vid basen av död tall.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7453,22 +7450,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Grimhild Angertuva</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118484672</v>
+        <v>118483227</v>
       </c>
       <c r="B59" t="n">
-        <v>94627</v>
+        <v>57443</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7477,46 +7474,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Angertuvan - Risveden, Vg</t>
+          <t>Skår, Vg</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>338400</v>
+        <v>338294</v>
       </c>
       <c r="R59" t="n">
-        <v>6433392</v>
+        <v>6433559</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7543,17 +7544,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7562,19 +7558,18 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7693,10 +7688,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118484390</v>
+        <v>118484672</v>
       </c>
       <c r="B61" t="n">
-        <v>57306</v>
+        <v>94627</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7705,31 +7700,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7737,10 +7736,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>338446</v>
+        <v>338400</v>
       </c>
       <c r="R61" t="n">
-        <v>6433213</v>
+        <v>6433392</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7777,7 +7776,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färskt spår av födosökande spillkråka på tallved.</t>
+          <t>2 kuddar, ungefär 40x25 (uppskattat) cm tillsammans</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7786,6 +7785,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8030,7 +8030,7 @@
         <v>121155035</v>
       </c>
       <c r="B64" t="n">
-        <v>97017</v>
+        <v>97027</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8030,7 +8030,7 @@
         <v>121155035</v>
       </c>
       <c r="B64" t="n">
-        <v>97027</v>
+        <v>97040</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8030,7 +8030,7 @@
         <v>121155035</v>
       </c>
       <c r="B64" t="n">
-        <v>97040</v>
+        <v>97041</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8030,7 +8030,7 @@
         <v>121155035</v>
       </c>
       <c r="B64" t="n">
-        <v>97041</v>
+        <v>97044</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8030,7 +8030,7 @@
         <v>121155035</v>
       </c>
       <c r="B64" t="n">
-        <v>97044</v>
+        <v>97050</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8030,7 +8030,7 @@
         <v>121155035</v>
       </c>
       <c r="B64" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8153,10 +8153,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123639932</v>
+        <v>123639306</v>
       </c>
       <c r="B65" t="n">
-        <v>94790</v>
+        <v>58132</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8165,31 +8165,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2810</v>
+        <v>103042</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8197,10 +8209,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>338319</v>
+        <v>338358</v>
       </c>
       <c r="R65" t="n">
-        <v>6433540</v>
+        <v>6433564</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8241,7 +8253,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8265,10 +8276,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123639306</v>
+        <v>123639932</v>
       </c>
       <c r="B66" t="n">
-        <v>58126</v>
+        <v>94807</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8277,43 +8288,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103042</v>
+        <v>2810</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8321,10 +8320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>338358</v>
+        <v>338319</v>
       </c>
       <c r="R66" t="n">
-        <v>6433564</v>
+        <v>6433540</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8365,6 +8364,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8385,6 +8385,244 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123756792</v>
+      </c>
+      <c r="B67" t="n">
+        <v>58132</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ale Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>338347</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6433525</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>123756637</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57503</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ale Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>338318</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6433460</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8156,7 +8156,7 @@
         <v>123639306</v>
       </c>
       <c r="B65" t="n">
-        <v>58132</v>
+        <v>58135</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>123639932</v>
       </c>
       <c r="B66" t="n">
-        <v>94807</v>
+        <v>94813</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>123756792</v>
       </c>
       <c r="B67" t="n">
-        <v>58132</v>
+        <v>58135</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>123756637</v>
       </c>
       <c r="B68" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8156,7 +8156,7 @@
         <v>123639306</v>
       </c>
       <c r="B65" t="n">
-        <v>58135</v>
+        <v>58136</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>123639932</v>
       </c>
       <c r="B66" t="n">
-        <v>94813</v>
+        <v>94815</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8388,10 +8388,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123756792</v>
+        <v>123756637</v>
       </c>
       <c r="B67" t="n">
-        <v>58135</v>
+        <v>57507</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8400,20 +8400,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8430,7 +8430,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>338347</v>
+        <v>338318</v>
       </c>
       <c r="R67" t="n">
-        <v>6433525</v>
+        <v>6433460</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123756637</v>
+        <v>123756792</v>
       </c>
       <c r="B68" t="n">
-        <v>57506</v>
+        <v>58136</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8519,20 +8519,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8549,7 +8549,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>338318</v>
+        <v>338347</v>
       </c>
       <c r="R68" t="n">
-        <v>6433460</v>
+        <v>6433525</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8388,10 +8388,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123756637</v>
+        <v>123756792</v>
       </c>
       <c r="B67" t="n">
-        <v>57529</v>
+        <v>58158</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8400,20 +8400,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8430,7 +8430,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>338318</v>
+        <v>338347</v>
       </c>
       <c r="R67" t="n">
-        <v>6433460</v>
+        <v>6433525</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123756792</v>
+        <v>123756637</v>
       </c>
       <c r="B68" t="n">
-        <v>58158</v>
+        <v>57529</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8519,20 +8519,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8549,7 +8549,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>338347</v>
+        <v>338318</v>
       </c>
       <c r="R68" t="n">
-        <v>6433525</v>
+        <v>6433460</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8629,7 +8629,7 @@
         <v>127087774</v>
       </c>
       <c r="B69" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8629,7 +8629,7 @@
         <v>127087774</v>
       </c>
       <c r="B69" t="n">
-        <v>58520</v>
+        <v>58522</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8731,6 +8731,984 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127837938</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97333</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>338338</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6433281</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127837895</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>338352</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6433276</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127838345</v>
+      </c>
+      <c r="B72" t="n">
+        <v>96058</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>338289</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6433246</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127838089</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58340</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>338347</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6433307</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127837764</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97333</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>338372</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6433259</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127839614</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58522</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>338359</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6433222</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127837864</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97333</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>338352</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6433279</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127838327</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97333</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>338285</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6433246</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer  Sumpskog</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128057754</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, Vg</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>338485</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6433412</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8629,7 +8629,7 @@
         <v>127087774</v>
       </c>
       <c r="B69" t="n">
-        <v>58522</v>
+        <v>58525</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>127837938</v>
       </c>
       <c r="B70" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>127837895</v>
       </c>
       <c r="B71" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B72" t="n">
-        <v>96058</v>
+        <v>58343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,37 +8958,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R72" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9017,7 +9022,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9027,7 +9032,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9054,10 +9059,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B73" t="n">
-        <v>58340</v>
+        <v>96061</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9065,42 +9070,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R73" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9169,7 +9169,7 @@
         <v>127837764</v>
       </c>
       <c r="B74" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9273,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127839614</v>
+        <v>127837864</v>
       </c>
       <c r="B75" t="n">
-        <v>58522</v>
+        <v>97336</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338359</v>
+        <v>338352</v>
       </c>
       <c r="R75" t="n">
-        <v>6433222</v>
+        <v>6433279</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127837864</v>
+        <v>127839614</v>
       </c>
       <c r="B76" t="n">
-        <v>97333</v>
+        <v>58525</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338352</v>
+        <v>338359</v>
       </c>
       <c r="R76" t="n">
-        <v>6433279</v>
+        <v>6433222</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9490,7 +9490,7 @@
         <v>127838327</v>
       </c>
       <c r="B77" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8736,7 +8736,7 @@
         <v>127837938</v>
       </c>
       <c r="B70" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>127837895</v>
       </c>
       <c r="B71" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>127838089</v>
       </c>
       <c r="B72" t="n">
-        <v>58343</v>
+        <v>58349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>127838345</v>
       </c>
       <c r="B73" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>127837764</v>
       </c>
       <c r="B74" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9273,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127837864</v>
+        <v>127839614</v>
       </c>
       <c r="B75" t="n">
-        <v>97336</v>
+        <v>58531</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338352</v>
+        <v>338359</v>
       </c>
       <c r="R75" t="n">
-        <v>6433279</v>
+        <v>6433222</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127839614</v>
+        <v>127837864</v>
       </c>
       <c r="B76" t="n">
-        <v>58525</v>
+        <v>97344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338359</v>
+        <v>338352</v>
       </c>
       <c r="R76" t="n">
-        <v>6433222</v>
+        <v>6433279</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9490,7 +9490,7 @@
         <v>127838327</v>
       </c>
       <c r="B77" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>128057754</v>
       </c>
       <c r="B78" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8736,7 +8736,7 @@
         <v>127837938</v>
       </c>
       <c r="B70" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B72" t="n">
-        <v>58349</v>
+        <v>96070</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,42 +8958,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R72" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9022,7 +9017,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9032,7 +9027,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9059,10 +9054,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B73" t="n">
-        <v>96069</v>
+        <v>58349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9070,37 +9065,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R73" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9169,7 +9169,7 @@
         <v>127837764</v>
       </c>
       <c r="B74" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>127837864</v>
       </c>
       <c r="B76" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>127838327</v>
       </c>
       <c r="B77" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B72" t="n">
-        <v>96070</v>
+        <v>58349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,37 +8958,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R72" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9017,7 +9022,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9027,7 +9032,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9054,10 +9059,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B73" t="n">
-        <v>58349</v>
+        <v>96070</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9065,42 +9070,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R73" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8736,7 +8736,7 @@
         <v>127837938</v>
       </c>
       <c r="B70" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>127838345</v>
       </c>
       <c r="B73" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>127837764</v>
       </c>
       <c r="B74" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>127837864</v>
       </c>
       <c r="B76" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>127838327</v>
       </c>
       <c r="B77" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8736,7 +8736,7 @@
         <v>127837938</v>
       </c>
       <c r="B70" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B72" t="n">
-        <v>58349</v>
+        <v>96072</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,42 +8958,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R72" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9022,7 +9017,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9032,7 +9027,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9059,10 +9054,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B73" t="n">
-        <v>96071</v>
+        <v>58349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9070,37 +9065,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R73" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9169,7 +9169,7 @@
         <v>127837764</v>
       </c>
       <c r="B74" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>127837864</v>
       </c>
       <c r="B76" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>127838327</v>
       </c>
       <c r="B77" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9273,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127839614</v>
+        <v>127837864</v>
       </c>
       <c r="B75" t="n">
-        <v>58531</v>
+        <v>97347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338359</v>
+        <v>338352</v>
       </c>
       <c r="R75" t="n">
-        <v>6433222</v>
+        <v>6433279</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127837864</v>
+        <v>127839614</v>
       </c>
       <c r="B76" t="n">
-        <v>97347</v>
+        <v>58531</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338352</v>
+        <v>338359</v>
       </c>
       <c r="R76" t="n">
-        <v>6433279</v>
+        <v>6433222</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B72" t="n">
-        <v>96072</v>
+        <v>58349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,37 +8958,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R72" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9017,7 +9022,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9027,7 +9032,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9054,10 +9059,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B73" t="n">
-        <v>58349</v>
+        <v>96072</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9065,42 +9070,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R73" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9273,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127837864</v>
+        <v>127839614</v>
       </c>
       <c r="B75" t="n">
-        <v>97347</v>
+        <v>58531</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338352</v>
+        <v>338359</v>
       </c>
       <c r="R75" t="n">
-        <v>6433279</v>
+        <v>6433222</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127839614</v>
+        <v>127837864</v>
       </c>
       <c r="B76" t="n">
-        <v>58531</v>
+        <v>97347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338359</v>
+        <v>338352</v>
       </c>
       <c r="R76" t="n">
-        <v>6433222</v>
+        <v>6433279</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B72" t="n">
-        <v>58349</v>
+        <v>96072</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,42 +8958,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R72" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9022,7 +9017,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9032,7 +9027,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9059,10 +9054,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B73" t="n">
-        <v>96072</v>
+        <v>58349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9070,37 +9065,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R73" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8736,7 +8736,7 @@
         <v>127837938</v>
       </c>
       <c r="B70" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>127837895</v>
       </c>
       <c r="B71" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B72" t="n">
-        <v>96072</v>
+        <v>58350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,37 +8958,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R72" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9017,7 +9022,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9027,7 +9032,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9054,10 +9059,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B73" t="n">
-        <v>58349</v>
+        <v>96080</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9065,42 +9070,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R73" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9169,7 +9169,7 @@
         <v>127837764</v>
       </c>
       <c r="B74" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>127837864</v>
       </c>
       <c r="B75" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>127839614</v>
       </c>
       <c r="B76" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>127838327</v>
       </c>
       <c r="B77" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>128057754</v>
       </c>
       <c r="B78" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -8736,7 +8736,7 @@
         <v>127837938</v>
       </c>
       <c r="B70" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>127837895</v>
       </c>
       <c r="B71" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127838089</v>
+        <v>127838345</v>
       </c>
       <c r="B72" t="n">
-        <v>58350</v>
+        <v>96173</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8958,42 +8958,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>338347</v>
+        <v>338289</v>
       </c>
       <c r="R72" t="n">
-        <v>6433307</v>
+        <v>6433246</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9022,7 +9017,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9032,7 +9027,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9059,10 +9054,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127838345</v>
+        <v>127838089</v>
       </c>
       <c r="B73" t="n">
-        <v>96080</v>
+        <v>58362</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9070,37 +9065,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skår, Skår, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>338289</v>
+        <v>338347</v>
       </c>
       <c r="R73" t="n">
-        <v>6433246</v>
+        <v>6433307</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9169,7 +9169,7 @@
         <v>127837764</v>
       </c>
       <c r="B74" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9273,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127837864</v>
+        <v>127839614</v>
       </c>
       <c r="B75" t="n">
-        <v>97355</v>
+        <v>58544</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338352</v>
+        <v>338359</v>
       </c>
       <c r="R75" t="n">
-        <v>6433279</v>
+        <v>6433222</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127839614</v>
+        <v>127837864</v>
       </c>
       <c r="B76" t="n">
-        <v>58532</v>
+        <v>97448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338359</v>
+        <v>338352</v>
       </c>
       <c r="R76" t="n">
-        <v>6433222</v>
+        <v>6433279</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9490,7 +9490,7 @@
         <v>127838327</v>
       </c>
       <c r="B77" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>128057754</v>
       </c>
       <c r="B78" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9273,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127839614</v>
+        <v>127837864</v>
       </c>
       <c r="B75" t="n">
-        <v>58544</v>
+        <v>97448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338359</v>
+        <v>338352</v>
       </c>
       <c r="R75" t="n">
-        <v>6433222</v>
+        <v>6433279</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127837864</v>
+        <v>127839614</v>
       </c>
       <c r="B76" t="n">
-        <v>97448</v>
+        <v>58544</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338352</v>
+        <v>338359</v>
       </c>
       <c r="R76" t="n">
-        <v>6433279</v>
+        <v>6433222</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9709,6 +9709,467 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128642893</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97449</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>338355</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6433567</v>
+      </c>
+      <c r="S79" t="n">
+        <v>8</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128636569</v>
+      </c>
+      <c r="B80" t="n">
+        <v>95814</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Ale/Skår, Ale/Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>338484</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6433363</v>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128637195</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98572</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ale/Skår, Ale/Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>338503</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6433388</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Naturskog, tidigare skogsbetad</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128635872</v>
+      </c>
+      <c r="B82" t="n">
+        <v>96174</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skår, Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>338417</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6433326</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9273,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127837864</v>
+        <v>127839614</v>
       </c>
       <c r="B75" t="n">
-        <v>97448</v>
+        <v>58544</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9284,21 +9284,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>338352</v>
+        <v>338359</v>
       </c>
       <c r="R75" t="n">
-        <v>6433279</v>
+        <v>6433222</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9380,10 +9380,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127839614</v>
+        <v>127837864</v>
       </c>
       <c r="B76" t="n">
-        <v>58544</v>
+        <v>97448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9415,10 +9415,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>338359</v>
+        <v>338352</v>
       </c>
       <c r="R76" t="n">
-        <v>6433222</v>
+        <v>6433279</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97449</v>
+        <v>97454</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95814</v>
+        <v>95819</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96174</v>
+        <v>96179</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9602,7 +9602,7 @@
         <v>128057754</v>
       </c>
       <c r="B78" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95819</v>
+        <v>95825</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95825</v>
+        <v>95827</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95827</v>
+        <v>95828</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10169,6 +10169,154 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128814800</v>
+      </c>
+      <c r="B83" t="n">
+        <v>56563</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>338331</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6433529</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Intill sumpskog</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Intill sumpskog</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95828</v>
+        <v>95855</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>128814800</v>
       </c>
       <c r="B83" t="n">
-        <v>56563</v>
+        <v>56590</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95855</v>
+        <v>95861</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95861</v>
+        <v>95868</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>128814800</v>
       </c>
       <c r="B83" t="n">
-        <v>56590</v>
+        <v>56593</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10318,6 +10318,230 @@
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128994838</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92836</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Angertuvan - Risveden, Angertuvan - Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>338303</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6433558</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På häll med tallar</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128994364</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Angertuvan - Risveden, Angertuvan - Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>338303</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6433558</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färaka spår vid basen av död gran</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>128814800</v>
       </c>
       <c r="B83" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>128994364</v>
       </c>
       <c r="B85" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95882</v>
+        <v>95887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95887</v>
+        <v>95895</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -9714,7 +9714,7 @@
         <v>128642893</v>
       </c>
       <c r="B79" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>128636569</v>
       </c>
       <c r="B80" t="n">
-        <v>95895</v>
+        <v>95905</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>128637195</v>
       </c>
       <c r="B81" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>128635872</v>
       </c>
       <c r="B82" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>128814800</v>
       </c>
       <c r="B83" t="n">
-        <v>56596</v>
+        <v>56598</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>128994364</v>
       </c>
       <c r="B85" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10175,7 +10175,7 @@
         <v>128814800</v>
       </c>
       <c r="B83" t="n">
-        <v>56598</v>
+        <v>56600</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>128994364</v>
       </c>
       <c r="B85" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 13111-2022 artfynd.xlsx
+++ b/artfynd/A 13111-2022 artfynd.xlsx
@@ -10323,7 +10323,7 @@
         <v>128994838</v>
       </c>
       <c r="B84" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
